--- a/backend/Files/Biblio/BooksWV.xlsx
+++ b/backend/Files/Biblio/BooksWV.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\APPS\SIMPLE\Parapreceptor\Ghost_Writer_v1 (Html)\backend\Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\APPS\SIMPLE\Parapreceptor\Ghost_Writer_v5\backend\Files\Biblio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D1FD98E-36D1-4641-96B7-005F10212DBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F876CBFE-69A6-4F7E-88E5-10E8AF7A5090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="25416" xr2:uid="{8C43181E-41E2-4285-98AA-22B67AB52120}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="153">
   <si>
     <t>Vieira, Waldo</t>
   </si>
@@ -62,12 +62,6 @@
     <t>700 Experimentos da Conscienciologia</t>
   </si>
   <si>
-    <t>1.058 p.; 40 seções; 100 subseções; 700 caps.; 147 abrevs.; 1 cronologia; 100 datas; 1 E-mail; 600 enus.; 272 estrangeirismos; 2 tabs.; 300 testes; glos. 280 termos; 5.116 refs.; alf.; geo.; ono.; 28,5 x 21,5 x 7 cm; enc.; Instituto Internacional de Projeciologia; Rio de Janeiro, RJ</t>
-  </si>
-  <si>
-    <t>**Vieira**, Waldo; ***700 Experimentos da Conscienciologia***; *Livro*; 1.058 p.; 40 seções; 100 subseções; 700 caps.; 147 abrevs.; 1 cronologia; 100 datas; 1 E-mail; 600 enus.; 272 estrangeirismos; 2 tabs.; 300 testes; glos. 280 termos; 5.116 refs.; alf.; geo.; ono.; 28,5 x 21,5 x 7 cm; enc.; Instituto Internacional de Projeciologia; Rio de Janeiro, RJ; 1994</t>
-  </si>
-  <si>
     <t>revisores Ana Maria Bonfim; Everton Santos; &amp; Tatiana Lopes; 1.088 p.; 40 seções; 100 subseções; 700 caps.; 147 abrevs.; 1 blog; 1 cronologia; 100 datas; 20 E-mails; 600 enus.; 272 estrangeirismos; 1 fórmula; 1 foto; 1 microbiografia; 56 tabs.; 57 técnicas; 300 testes; 21 websites; glos. 280 termos; 5.116 refs.; alf.; geo.; ono.; 28,5 x 21,5 x 7 cm; enc.; 3ª Ed. rev. e amp.; Associação Internacional Editares; Foz do Iguaçu, PR</t>
   </si>
   <si>
@@ -264,9 +258,6 @@
   </si>
   <si>
     <t>Centro de Altos Estudos da Conscienciologia (CEAEC)</t>
-  </si>
-  <si>
-    <t>1.058 p.; 40 seções; 100 subseções; 700 caps.; 28,5 x 21,5 x 7 cm; enc.</t>
   </si>
   <si>
     <t xml:space="preserve"> 260 p.; 200 caps.; 21 x 14 cm; br.</t>
@@ -506,9 +497,6 @@
   </si>
   <si>
     <t>**Vieira**, Waldo; ***Conscienciograma: Técnica de Avaliação da Consciência Integral***; 344 p.; 150 abrevs.; 106 assuntos das folhas de avaliação; 21 x 14 cm; br.; *Instituto Internacional de Projeciologia* (IIP); Rio de Janeiro, RJ; 1996</t>
-  </si>
-  <si>
-    <t>**Vieira**, Waldo; ***700 Experimentos da Conscienciologia***; 1.058 p.; 40 seções; 100 subseções; 700 caps.; 28,5 x 21,5 x 7 cm; enc.; *Instituto Internacional de Projeciologia e Conscienciologia* (IIPC); Rio de Janeiro, RJ; 1994</t>
   </si>
 </sst>
 </file>
@@ -1096,7 +1084,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80B9D723-500C-46BE-904F-6FFE829F75C8}">
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="43.5546875" customWidth="1"/>
@@ -1113,35 +1101,35 @@
   <sheetData>
     <row r="1" spans="1:11" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="I1" s="2"/>
       <c r="J1" s="25" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K1" s="26" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
@@ -1149,73 +1137,73 @@
         <v>0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C2" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H2" s="7">
         <v>1992</v>
       </c>
       <c r="I2" s="8"/>
       <c r="J2" s="16" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="K2" s="17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" s="9" customFormat="1" ht="32.4" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C3" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H3" s="7">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="I3" s="8"/>
       <c r="J3" s="16" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="K3" s="17" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="9" customFormat="1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>12</v>
+        <v>107</v>
       </c>
       <c r="C4" s="22" t="s">
         <v>2</v>
@@ -1224,56 +1212,56 @@
         <v>13</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H4" s="7">
         <v>1996</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="16" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="K4" s="17" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="9" customFormat="1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H5" s="7">
         <v>1996</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="16" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="K5" s="17" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
@@ -1281,29 +1269,29 @@
         <v>0</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C6" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H6" s="7">
         <v>1996</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="16" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="K6" s="17" t="s">
         <v>48</v>
@@ -1314,98 +1302,98 @@
         <v>0</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="C7" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H7" s="7">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="16" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="K7" s="17" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" s="9" customFormat="1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>1</v>
+        <v>106</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H8" s="7">
         <v>1997</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="16" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="K8" s="17" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" s="9" customFormat="1" ht="32.4" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>109</v>
+        <v>64</v>
       </c>
       <c r="C9" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H9" s="7">
         <v>1997</v>
       </c>
       <c r="I9" s="8"/>
       <c r="J9" s="16" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="K9" s="17" t="s">
-        <v>6</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
@@ -1413,32 +1401,32 @@
         <v>0</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="C10" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>70</v>
       </c>
       <c r="H10" s="7">
-        <v>1997</v>
+        <v>2002</v>
       </c>
       <c r="I10" s="8"/>
       <c r="J10" s="16" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K10" s="17" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
@@ -1446,98 +1434,98 @@
         <v>0</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C11" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H11" s="7">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="I11" s="8"/>
       <c r="J11" s="16" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="K11" s="17" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>26</v>
+        <v>122</v>
       </c>
       <c r="C12" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H12" s="7">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="I12" s="8"/>
       <c r="J12" s="16" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K12" s="17" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="9" customFormat="1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>125</v>
+        <v>21</v>
       </c>
       <c r="C13" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H13" s="7">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="I13" s="8"/>
       <c r="J13" s="16" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="K13" s="17" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="9" customFormat="1" ht="32.4" x14ac:dyDescent="0.3">
@@ -1545,32 +1533,32 @@
         <v>0</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C14" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H14" s="7">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="I14" s="8"/>
       <c r="J14" s="16" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="9" customFormat="1" ht="32.4" x14ac:dyDescent="0.3">
@@ -1578,65 +1566,65 @@
         <v>0</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="C15" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H15" s="7">
         <v>2009</v>
       </c>
       <c r="I15" s="8"/>
       <c r="J15" s="16" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="K15" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" s="9" customFormat="1" ht="32.4" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="C16" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H16" s="7">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="I16" s="8"/>
       <c r="J16" s="16" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="K16" s="17" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
@@ -1644,32 +1632,32 @@
         <v>0</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="C17" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H17" s="7">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="I17" s="8"/>
       <c r="J17" s="16" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="K17" s="17" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
@@ -1677,7 +1665,7 @@
         <v>0</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C18" s="22" t="s">
         <v>2</v>
@@ -1686,20 +1674,20 @@
         <v>36</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H18" s="7">
         <v>2011</v>
       </c>
       <c r="I18" s="8"/>
       <c r="J18" s="16" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="K18" s="17" t="s">
         <v>37</v>
@@ -1710,32 +1698,32 @@
         <v>0</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>124</v>
+        <v>31</v>
       </c>
       <c r="C19" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H19" s="7">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="I19" s="8"/>
       <c r="J19" s="16" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="K19" s="17" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
@@ -1743,32 +1731,32 @@
         <v>0</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C20" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H20" s="7">
         <v>2012</v>
       </c>
       <c r="I20" s="8"/>
       <c r="J20" s="16" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="K20" s="17" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
@@ -1776,32 +1764,32 @@
         <v>0</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="C21" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H21" s="7">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="I21" s="8"/>
       <c r="J21" s="16" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="K21" s="17" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
@@ -1809,32 +1797,32 @@
         <v>0</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>7</v>
+        <v>119</v>
       </c>
       <c r="C22" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H22" s="7">
         <v>2013</v>
       </c>
       <c r="I22" s="8"/>
       <c r="J22" s="16" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="K22" s="17" t="s">
-        <v>11</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
@@ -1842,32 +1830,32 @@
         <v>0</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>122</v>
+        <v>15</v>
       </c>
       <c r="C23" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H23" s="7">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="I23" s="8"/>
       <c r="J23" s="16" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="K23" s="17" t="s">
-        <v>63</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
@@ -1875,32 +1863,32 @@
         <v>0</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H24" s="7">
         <v>2014</v>
       </c>
       <c r="I24" s="8"/>
       <c r="J24" s="16" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="K24" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
@@ -1908,172 +1896,139 @@
         <v>0</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>102</v>
+        <v>2</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>83</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H25" s="7">
         <v>2014</v>
       </c>
       <c r="I25" s="8"/>
       <c r="J25" s="16" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K25" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" s="9" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" s="15" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C26" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="H26" s="13">
+        <v>2019</v>
+      </c>
+      <c r="I26" s="14"/>
+      <c r="J26" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="K26" s="18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" s="9" customFormat="1" ht="64.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="H29" s="7">
+        <v>2023</v>
+      </c>
+      <c r="I29" s="8"/>
+      <c r="J29" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="C26" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H26" s="7">
-        <v>2014</v>
-      </c>
-      <c r="I26" s="8"/>
-      <c r="J26" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="K26" s="17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" s="15" customFormat="1" ht="21.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="C27" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="F27" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="G27" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="H27" s="13">
-        <v>2019</v>
-      </c>
-      <c r="I27" s="14"/>
-      <c r="J27" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="K27" s="18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" s="9" customFormat="1" ht="64.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B30" s="5" t="s">
+      <c r="K29" s="27" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" s="9" customFormat="1" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C30" s="22" t="s">
-        <v>101</v>
-      </c>
-      <c r="D30" s="9" t="s">
+      <c r="C31" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="I31" s="8"/>
+      <c r="J31" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="E30" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H30" s="7">
-        <v>2023</v>
-      </c>
-      <c r="I30" s="8"/>
-      <c r="J30" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="K30" s="27" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" s="9" customFormat="1" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C32" s="22" t="s">
-        <v>101</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="I32" s="8"/>
-      <c r="J32" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="K32" s="17" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="34" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D34" s="6"/>
-    </row>
-    <row r="40" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D40" s="20"/>
+      <c r="K31" s="17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D33" s="6"/>
+    </row>
+    <row r="39" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D39" s="20"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K28">
-    <sortCondition ref="H2:H28"/>
-    <sortCondition ref="B2:B28"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K27">
+    <sortCondition ref="H2:H27"/>
+    <sortCondition ref="B2:B27"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
